--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486897_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486897_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3546</v>
+        <v>12.464</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9562</v>
+        <v>10.9175</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3983</v>
+        <v>1.5465</v>
       </c>
       <c r="G2" t="n">
         <v>8.5854</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9046999999999999</v>
+        <v>1.0142</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9568</v>
+        <v>0.918</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0521</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.8378</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.6523</v>
+        <v>7.2966</v>
       </c>
       <c r="E3" t="n">
         <v>4.271</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3813</v>
+        <v>3.0256</v>
       </c>
       <c r="G3" t="n">
         <v>5.1221</v>
@@ -688,13 +688,13 @@
         <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9408</v>
+        <v>0.5851</v>
       </c>
       <c r="T3" t="n">
         <v>0.3757</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5651</v>
+        <v>0.2094</v>
       </c>
       <c r="V3" t="n">
         <v>0.768</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8778</v>
+        <v>4.5985</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2405</v>
+        <v>2.7833</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6373</v>
+        <v>1.8152</v>
       </c>
       <c r="G4" t="n">
         <v>1.2437</v>
@@ -766,13 +766,13 @@
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3815</v>
+        <v>1.1022</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0962</v>
+        <v>0.6391</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2853</v>
+        <v>0.4631</v>
       </c>
       <c r="V4" t="n">
         <v>1.6366</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6708</v>
+        <v>4.2694</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0513</v>
+        <v>5.2194</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6194</v>
+        <v>-0.95</v>
       </c>
       <c r="G5" t="n">
-        <v>1.859</v>
+        <v>3.4063</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2306</v>
+        <v>0.4993</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6284</v>
+        <v>2.9071</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2767</v>
+        <v>4.5368</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7226</v>
+        <v>1.0512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9993</v>
+        <v>3.4857</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5823</v>
+        <v>-1.1305</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9532</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6291</v>
+        <v>-0.5786</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1259</v>
+        <v>0.8282</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8013</v>
+        <v>0.4958</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3246</v>
+        <v>0.3324</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0698</v>
+        <v>0.2402</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0698</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1879</v>
+        <v>3.8496</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0489</v>
+        <v>0.3191</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8611</v>
+        <v>3.5305</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4063</v>
+        <v>1.859</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4993</v>
+        <v>0.2306</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9071</v>
+        <v>1.6284</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5368</v>
+        <v>0.2767</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0512</v>
+        <v>-0.7226</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4857</v>
+        <v>0.9993</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1305</v>
+        <v>1.5823</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.9532</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5786</v>
+        <v>0.6291</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7466</v>
+        <v>1.3047</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3253</v>
+        <v>1.0691</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4213</v>
+        <v>0.2356</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2402</v>
+        <v>0.0698</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>0.0698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3832</v>
+        <v>3.7569</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0176</v>
+        <v>2.9666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3657</v>
+        <v>0.7904</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9899</v>
+        <v>4.4601</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1715</v>
+        <v>2.7868</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1816</v>
+        <v>1.6733</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6574</v>
+        <v>3.1015</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3286</v>
+        <v>1.9179</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6713</v>
+        <v>1.1836</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3325</v>
+        <v>1.3586</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8428</v>
+        <v>0.8689</v>
       </c>
       <c r="O7" t="n">
         <v>0.4897</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2321</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q7" t="n">
+        <v>-2.2588</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.0267</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5289</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.1761</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.2321</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.0997</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.0203</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.9384</v>
-      </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0808</v>
+        <v>3.3989</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5869</v>
+        <v>3.1222</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4939</v>
+        <v>0.2768</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4601</v>
+        <v>3.9899</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7868</v>
+        <v>4.1715</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6733</v>
+        <v>-0.1816</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1015</v>
+        <v>2.6574</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9179</v>
+        <v>3.3286</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1836</v>
+        <v>-0.6713</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3586</v>
+        <v>1.3325</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8689</v>
+        <v>0.8428</v>
       </c>
       <c r="O8" t="n">
         <v>0.4897</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2321</v>
+        <v>1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1472</v>
+        <v>0.1154</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3253</v>
+        <v>0.2246</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4725</v>
+        <v>-0.1092</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.9384</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4189</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4189</v>
+        <v>-2.1786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5831</v>
+        <v>2.527</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2678</v>
+        <v>3.0402</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3154</v>
+        <v>-0.5132</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7539</v>
+        <v>1.6349</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6957</v>
+        <v>1.5085</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9418</v>
+        <v>0.1264</v>
       </c>
       <c r="J9" t="n">
-        <v>2.298</v>
+        <v>3.1915</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2191</v>
+        <v>1.8366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0789</v>
+        <v>1.3549</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5441</v>
+        <v>-1.5566</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4766</v>
+        <v>-0.3281</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0208</v>
+        <v>-1.2284</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0613</v>
+        <v>-0.0649</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1822</v>
+        <v>-0.1513</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2435</v>
+        <v>0.0864</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1786</v>
+        <v>-0.4805</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0197</v>
+        <v>2.4366</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6218</v>
+        <v>2.477</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6022</v>
+        <v>-0.0404</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6349</v>
+        <v>1.7539</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5085</v>
+        <v>2.6957</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1264</v>
+        <v>-0.9418</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1915</v>
+        <v>2.298</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8366</v>
+        <v>2.2191</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3549</v>
+        <v>0.0789</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5566</v>
+        <v>-0.5441</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3281</v>
+        <v>0.4766</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2284</v>
+        <v>-1.0208</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4374</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q10" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.0852</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.1122</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4374</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.5722</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.5697</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.4805</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.4805</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4194</v>
+        <v>-0.4145</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6666</v>
+        <v>-0.8099</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2472</v>
+        <v>0.3954</v>
       </c>
       <c r="G11" t="n">
         <v>-2.123</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3196</v>
+        <v>0.3245</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3098</v>
+        <v>0.1665</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0098</v>
+        <v>0.158</v>
       </c>
       <c r="V11" t="n">
         <v>1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2438</v>
+        <v>-0.7068</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1151</v>
+        <v>-1.6967</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8713</v>
+        <v>0.9898</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8076</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8818</v>
+        <v>-0.3448</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5697</v>
+        <v>-0.1513</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3121</v>
+        <v>-0.1936</v>
       </c>
       <c r="V12" t="n">
         <v>0.4189</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>43.147</v>
+        <v>43.4762</v>
       </c>
       <c r="E13" t="n">
-        <v>32.2803</v>
+        <v>32.6097</v>
       </c>
       <c r="F13" t="n">
-        <v>10.8665</v>
+        <v>10.8666</v>
       </c>
       <c r="G13" t="n">
-        <v>28.12469999999999</v>
+        <v>28.1247</v>
       </c>
       <c r="H13" t="n">
         <v>17.6799</v>
@@ -1459,7 +1459,7 @@
         <v>-1.1418</v>
       </c>
       <c r="P13" t="n">
-        <v>5.1335</v>
+        <v>5.133500000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-6.160200000000001</v>
@@ -1468,22 +1468,22 @@
         <v>11.2939</v>
       </c>
       <c r="S13" t="n">
-        <v>4.9789</v>
+        <v>5.3083</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9888</v>
+        <v>4.3182</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9901000000000002</v>
+        <v>0.9899999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>4.909600000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.8622</v>
+        <v>8.862200000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.952599999999999</v>
+        <v>-3.9526</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2193</v>
+        <v>-1.1601</v>
       </c>
       <c r="E14" t="n">
         <v>0.4679</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6872</v>
+        <v>-1.6279</v>
       </c>
       <c r="G14" t="n">
         <v>-1.4431</v>
@@ -1546,13 +1546,13 @@
         <v>0.4107</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="T14" t="n">
         <v>-0.159</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1492</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1179</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.5023</v>
+        <v>-1.2129</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0982</v>
+        <v>1.3074</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6005</v>
+        <v>-2.5203</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4848</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3053</v>
+        <v>0.5947</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1358</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4411</v>
+        <v>0.5213</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9121</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.0327</v>
+        <v>-2.5863</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3532</v>
+        <v>1.144</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.3858</v>
+        <v>-3.7303</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1976</v>
@@ -1702,13 +1702,13 @@
         <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4852</v>
+        <v>-0.0388</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4957</v>
+        <v>0.2865</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9808</v>
+        <v>-0.3253</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1179</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.9403</v>
+        <v>-4.1146</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5626</v>
+        <v>-1.2948</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3777</v>
+        <v>-2.8199</v>
       </c>
       <c r="G17" t="n">
         <v>-5.0265</v>
@@ -1780,13 +1780,13 @@
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1667</v>
+        <v>-0.341</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8714</v>
+        <v>0.1392</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0381</v>
+        <v>-0.4802</v>
       </c>
       <c r="V17" t="n">
         <v>1.253</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.0275</v>
+        <v>-4.2761</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5957</v>
+        <v>-0.4911</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4318</v>
+        <v>-3.785</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8473</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4944</v>
+        <v>-0.743</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2094</v>
+        <v>-0.1048</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.285</v>
+        <v>-0.6382</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4805</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>D. JACKSON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1519</v>
+        <v>-4.4032</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3565</v>
+        <v>0.3636</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7954</v>
+        <v>-4.7668</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.2715</v>
+        <v>-6.0453</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8059</v>
+        <v>-4.7456</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4656</v>
+        <v>-1.2997</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.4995</v>
+        <v>-1.6876</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1436</v>
+        <v>-2.0555</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3559</v>
+        <v>0.3679</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.772</v>
+        <v>-4.3577</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6623</v>
+        <v>-2.6901</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1097</v>
+        <v>-1.6675</v>
       </c>
       <c r="P19" t="n">
         <v>-0.2053</v>
@@ -1936,28 +1936,28 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3595</v>
+        <v>-0.187</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9295</v>
+        <v>-0.3491</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4299</v>
+        <v>0.162</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0345</v>
+        <v>2.0345</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>3.427</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2747</v>
+        <v>-1.3926</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. JACKSON</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2418</v>
+        <v>-5.5916</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1544</v>
+        <v>-2.5509</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.3962</v>
+        <v>-3.0407</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.0453</v>
+        <v>-1.9242</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.7456</v>
+        <v>-0.9536</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2997</v>
+        <v>-0.9706</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6876</v>
+        <v>0.2454</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.0555</v>
+        <v>0.127</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3679</v>
+        <v>0.1184</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.3577</v>
+        <v>-2.1696</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.6901</v>
+        <v>-1.0807</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6675</v>
+        <v>-1.089</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0256</v>
+        <v>-0.4078</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5583</v>
+        <v>-0.3527</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4673</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0345</v>
+        <v>-3.6702</v>
       </c>
       <c r="W20" t="n">
-        <v>3.427</v>
+        <v>-2.4436</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3926</v>
+        <v>-1.2267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0648</v>
+        <v>-5.6523</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1785</v>
+        <v>-3.0887</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.8863</v>
+        <v>-2.5636</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9242</v>
+        <v>-5.2715</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9536</v>
+        <v>-2.8059</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9706</v>
+        <v>-2.4656</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2454</v>
+        <v>-2.4995</v>
       </c>
       <c r="K21" t="n">
-        <v>0.127</v>
+        <v>-2.1436</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1184</v>
+        <v>-0.3559</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1696</v>
+        <v>-2.772</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0807</v>
+        <v>-0.6623</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.089</v>
+        <v>-2.1097</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.881</v>
+        <v>0.8591</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9804</v>
+        <v>0.1973</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9006999999999999</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.6702</v>
+        <v>-1.0345</v>
       </c>
       <c r="W21" t="n">
-        <v>-2.4436</v>
+        <v>0.2402</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2267</v>
+        <v>-1.2747</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.9665</v>
+        <v>-9.9657</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.247</v>
+        <v>-6.724</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7194</v>
+        <v>-3.2417</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8844</v>
@@ -2170,13 +2170,13 @@
         <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5219</v>
+        <v>-0.5212</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2438</v>
+        <v>-0.7208</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.278</v>
+        <v>0.1996</v>
       </c>
       <c r="V22" t="n">
         <v>-1.864</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-43.14709999999999</v>
+        <v>-38.9628</v>
       </c>
       <c r="E23" t="n">
         <v>-10.8666</v>
       </c>
       <c r="F23" t="n">
-        <v>-32.2803</v>
+        <v>-28.0962</v>
       </c>
       <c r="G23" t="n">
         <v>-28.1247</v>
@@ -2248,13 +2248,13 @@
         <v>6.160400000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.979</v>
+        <v>-0.7948</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9901</v>
+        <v>-0.9900000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.988999999999999</v>
+        <v>0.1951000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-4.909599999999999</v>
